--- a/samples/coverage/ctosim_coverage.xlsx
+++ b/samples/coverage/ctosim_coverage.xlsx
@@ -982,7 +982,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>region=${region}</t>
+          <t>filter=${region}</t>
         </is>
       </c>
     </row>
